--- a/ProgramPartListWeb/Content/Uploads/FinalUploadTemplate.xlsx
+++ b/ProgramPartListWeb/Content/Uploads/FinalUploadTemplate.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllSystems\P1saproject\ProgramPartListWeb\Content\Uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaye-labandia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D275429-B03F-45C2-9C41-90845BCA5A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1733E7F9-C00A-497A-BB89-EBB600E72F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC1CEC74-1A76-44F7-8956-40BDC247BB65}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC1CEC74-1A76-44F7-8956-40BDC247BB65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$XEZ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
   <si>
     <t>LINE</t>
   </si>
@@ -84,6 +84,135 @@
   </si>
   <si>
     <t>Operation Number</t>
+  </si>
+  <si>
+    <t>P1SA-C</t>
+  </si>
+  <si>
+    <t>P1SA-W</t>
+  </si>
+  <si>
+    <t>P1SA-M</t>
+  </si>
+  <si>
+    <t>P1SA-R</t>
+  </si>
+  <si>
+    <t>P1FA-FA</t>
+  </si>
+  <si>
+    <t>P1FA-H</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>511058286490</t>
+  </si>
+  <si>
+    <t>00412145-01</t>
+  </si>
+  <si>
+    <t>９Ａ０９２４Ｈ４Ｄ０１Ｐ,SDC</t>
+  </si>
+  <si>
+    <t>FFACM</t>
+  </si>
+  <si>
+    <t>06/26/2026 09:15</t>
+  </si>
+  <si>
+    <t>FOR LINE 1</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>602130373670</t>
+  </si>
+  <si>
+    <t>00868128-01</t>
+  </si>
+  <si>
+    <t>９ＧＡ０４１２Ｐ７Ｇ００６Ｐ</t>
+  </si>
+  <si>
+    <t>06/21/2026 09:05</t>
+  </si>
+  <si>
+    <t>PLGNZ+407+7452+HC1000</t>
+  </si>
+  <si>
+    <t>IP / SHORT DEEMED SILICONE</t>
+  </si>
+  <si>
+    <t>604252104730</t>
+  </si>
+  <si>
+    <t>00917358-01</t>
+  </si>
+  <si>
+    <t>９ＨＶ０８１２Ｐ１Ｇ６０１１Ｐ,SSH</t>
+  </si>
+  <si>
+    <t>06/20/2026 08:56</t>
+  </si>
+  <si>
+    <t>OVEN+603</t>
+  </si>
+  <si>
+    <t>COMPLETED / INTS OK</t>
+  </si>
+  <si>
+    <t>511088365597</t>
+  </si>
+  <si>
+    <t>01199010-01</t>
+  </si>
+  <si>
+    <t>９ＨＶ０８１２Ｐ１Ｇ６１２１－ＳＰ, STW/CHEN_FC</t>
+  </si>
+  <si>
+    <t>06/14/2026 10:17</t>
+  </si>
+  <si>
+    <t>OVEN+603+2FAN</t>
+  </si>
+  <si>
+    <t>PENDING 154 PCS/ 95 UNREADABLE</t>
+  </si>
+  <si>
+    <t>606033029690</t>
+  </si>
+  <si>
+    <t>01130900-01</t>
+  </si>
+  <si>
+    <t>９ＲＡ１２１２Ｐ４Ｇ００１１Ｐ</t>
+  </si>
+  <si>
+    <t>FFACS</t>
+  </si>
+  <si>
+    <t>OVEN+1A27NSLU</t>
+  </si>
+  <si>
+    <t>IMP TO PACK</t>
+  </si>
+  <si>
+    <t>509157161210</t>
+  </si>
+  <si>
+    <t>06/15/2026 09:02</t>
+  </si>
+  <si>
+    <t>ONLINE ADHESIVE TO PACK CODE M (LIGHT BLUE)</t>
+  </si>
+  <si>
+    <t>P1SA-P</t>
   </si>
 </sst>
 </file>
@@ -93,7 +222,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,11 +263,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -170,8 +294,82 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Aptos Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Aptos Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,6 +379,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,17 +443,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -248,35 +483,151 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{DAAEB316-F7A5-4361-A596-999A2CB636FD}"/>
     <cellStyle name="Normal 2_OP-Final Assy Sched 032125" xfId="5" xr:uid="{4E0790A3-5751-463A-8AF2-93FC9BDDB334}"/>
     <cellStyle name="Normal 3 2 2 2 2 2 2 2" xfId="4" xr:uid="{FEA8C484-7775-4BDE-B973-B17394AF0A67}"/>
     <cellStyle name="Normal 3 3 2 2" xfId="2" xr:uid="{0B1BDE0A-FBDB-46D4-9306-DEED50060F09}"/>
+    <cellStyle name="Normal_Latest May 2011 Production Schedule rev 4" xfId="6" xr:uid="{7AC3ADAE-A174-4B81-AD22-F7D22CEB5562}"/>
     <cellStyle name="Normal_Sheet1 2 2" xfId="1" xr:uid="{A7067E42-9D69-4083-BFAB-4A493823FE00}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="9"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -586,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4959DBC-D362-41B9-9C4D-867EFED801DE}">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="7" customWidth="1"/>
@@ -602,12 +953,17 @@
     <col min="11" max="11" width="25.5703125" style="8" customWidth="1"/>
     <col min="12" max="12" width="8.28515625" style="10" customWidth="1"/>
     <col min="13" max="13" width="9.7109375" style="11" customWidth="1"/>
-    <col min="14" max="14" width="10" style="11" customWidth="1"/>
-    <col min="15" max="15" width="20.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="7"/>
+    <col min="14" max="14" width="10.28515625" style="11" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" style="11" customWidth="1"/>
+    <col min="16" max="16" width="10" style="11" customWidth="1"/>
+    <col min="17" max="17" width="14" style="11" customWidth="1"/>
+    <col min="18" max="20" width="14.85546875" style="11" customWidth="1"/>
+    <col min="21" max="22" width="12.42578125" style="11" customWidth="1"/>
+    <col min="23" max="23" width="20.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,12 +1006,323 @@
       <c r="N1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="12" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="16">
+        <v>112</v>
+      </c>
+      <c r="G2" s="18">
+        <v>46198</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="21">
+        <v>46199</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="23">
+        <v>46204</v>
+      </c>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="11">
+        <v>3</v>
+      </c>
+      <c r="W2" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="26">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="27">
+        <v>46193</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="30">
+        <v>46197</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="23">
+        <v>46204</v>
+      </c>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>500</v>
+      </c>
+      <c r="S3" s="11">
+        <v>8976</v>
+      </c>
+      <c r="W3" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="26">
+        <v>200</v>
+      </c>
+      <c r="G4" s="27">
+        <v>46193</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="30">
+        <v>46198</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="23">
+        <v>46204</v>
+      </c>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="11">
+        <v>2</v>
+      </c>
+      <c r="S4" s="11">
+        <v>653</v>
+      </c>
+      <c r="W4" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="26">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="32">
+        <v>46184</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="32">
+        <v>46191</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="Q5" s="11">
+        <v>300</v>
+      </c>
+      <c r="W5" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="16">
+        <v>90</v>
+      </c>
+      <c r="G6" s="18">
+        <v>46193</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="21">
+        <v>46196</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="38">
+        <v>46198</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="R6" s="11">
+        <v>6963</v>
+      </c>
+      <c r="W6" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="16">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="40">
+        <v>46188</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="42">
+        <v>46192</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="11">
+        <v>1000</v>
+      </c>
+      <c r="S7" s="11">
+        <v>444</v>
+      </c>
+      <c r="W7" s="43">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:XEZ1" xr:uid="{B4959DBC-D362-41B9-9C4D-867EFED801DE}"/>
+  <autoFilter ref="A1:C1" xr:uid="{B4959DBC-D362-41B9-9C4D-867EFED801DE}"/>
+  <conditionalFormatting sqref="A2:A7">
+    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
